--- a/SuppXLS/Scen_SYS_CarbonBudget-CAP24_CB1_2.xlsx
+++ b/SuppXLS/Scen_SYS_CarbonBudget-CAP24_CB1_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\Integrated saturation V1.1\AFOLU model\tim-leaf v1.0\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2558C4DC-E6FC-48EB-AE5B-487179A4CE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBC3DDC-4FDE-4C97-AB15-AA7B5129182B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="-16310" windowWidth="29020" windowHeight="15700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -9669,17 +9669,17 @@
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.36328125" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
     <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="38.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -9850,11 +9850,11 @@
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="2" max="2" width="32.54296875" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" customWidth="1"/>
     <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.36328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
